--- a/data/base/Backlog_4.xlsx
+++ b/data/base/Backlog_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78A309C5-8305-44B0-BA44-1BDFAF8946CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86BE1728-C565-4191-B485-288531801454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" activeTab="1" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="29">
   <si>
     <t>Backlog</t>
   </si>
@@ -125,6 +125,9 @@
   </si>
   <si>
     <t>Isabela Borchardt</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -681,7 +684,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12">
         <v>2026</v>
@@ -696,7 +699,7 @@
         <v>46059</v>
       </c>
       <c r="G3" s="12">
-        <v>8902</v>
+        <v>9594</v>
       </c>
       <c r="H3" s="14">
         <v>46023</v>
@@ -705,7 +708,7 @@
         <v>46055</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>11</v>
@@ -716,7 +719,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="12">
         <v>2026</v>
@@ -731,16 +734,16 @@
         <v>46059</v>
       </c>
       <c r="G4" s="12">
-        <v>9392</v>
+        <v>9914</v>
       </c>
       <c r="H4" s="14">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I4" s="13">
         <v>46055</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>11</v>
@@ -751,7 +754,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="12">
         <v>2026</v>
@@ -766,7 +769,7 @@
         <v>46059</v>
       </c>
       <c r="G5" s="12">
-        <v>9594</v>
+        <v>9392</v>
       </c>
       <c r="H5" s="14">
         <v>46023</v>
@@ -775,7 +778,7 @@
         <v>46055</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>11</v>
@@ -786,7 +789,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" s="12">
         <v>2026</v>
@@ -801,7 +804,7 @@
         <v>46059</v>
       </c>
       <c r="G6" s="12">
-        <v>9634</v>
+        <v>8902</v>
       </c>
       <c r="H6" s="14">
         <v>46023</v>
@@ -810,7 +813,7 @@
         <v>46055</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>11</v>
@@ -845,7 +848,7 @@
         <v>46055</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>11</v>
@@ -880,7 +883,7 @@
         <v>46055</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>11</v>
@@ -926,7 +929,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="12">
         <v>2026</v>
@@ -941,7 +944,7 @@
         <v>46059</v>
       </c>
       <c r="G10" s="12">
-        <v>9819</v>
+        <v>9878</v>
       </c>
       <c r="H10" s="14">
         <v>46023</v>
@@ -950,7 +953,7 @@
         <v>46055</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>11</v>
@@ -976,16 +979,16 @@
         <v>46059</v>
       </c>
       <c r="G11" s="12">
-        <v>9878</v>
+        <v>10131</v>
       </c>
       <c r="H11" s="14">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I11" s="13">
         <v>46055</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>11</v>
@@ -996,7 +999,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C12" s="12">
         <v>2026</v>
@@ -1011,7 +1014,7 @@
         <v>46059</v>
       </c>
       <c r="G12" s="12">
-        <v>9906</v>
+        <v>9819</v>
       </c>
       <c r="H12" s="14">
         <v>46023</v>
@@ -1020,7 +1023,7 @@
         <v>46055</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>11</v>
@@ -1031,7 +1034,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" s="12">
         <v>2026</v>
@@ -1046,10 +1049,10 @@
         <v>46059</v>
       </c>
       <c r="G13" s="12">
-        <v>9914</v>
+        <v>9634</v>
       </c>
       <c r="H13" s="14">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I13" s="13">
         <v>46055</v>
@@ -1090,7 +1093,7 @@
         <v>46055</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>11</v>
@@ -1101,7 +1104,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" s="12">
         <v>2026</v>
@@ -1116,16 +1119,16 @@
         <v>46059</v>
       </c>
       <c r="G15" s="12">
-        <v>10131</v>
+        <v>9906</v>
       </c>
       <c r="H15" s="14">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I15" s="13">
         <v>46055</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>11</v>
@@ -1343,7 +1346,11 @@
       <c r="I50" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}"/>
+  <autoFilter ref="A1:K15" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
+      <sortCondition ref="B1:B15"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1409,7 +1416,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C2" s="15">
         <v>2026</v>
@@ -1424,7 +1431,7 @@
         <v>46059</v>
       </c>
       <c r="G2" s="15">
-        <v>9140</v>
+        <v>9258</v>
       </c>
       <c r="H2" s="14">
         <v>46023</v>
@@ -1433,7 +1440,7 @@
         <v>46055</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>15</v>
@@ -1459,7 +1466,7 @@
         <v>46059</v>
       </c>
       <c r="G3" s="15">
-        <v>9258</v>
+        <v>9444</v>
       </c>
       <c r="H3" s="14">
         <v>46023</v>
@@ -1479,7 +1486,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C4" s="15">
         <v>2026</v>
@@ -1494,10 +1501,10 @@
         <v>46059</v>
       </c>
       <c r="G4" s="15">
-        <v>9262</v>
+        <v>9457</v>
       </c>
       <c r="H4" s="14">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I4" s="13">
         <v>46055</v>
@@ -1538,7 +1545,7 @@
         <v>46055</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K5" s="15" t="s">
         <v>15</v>
@@ -1573,7 +1580,7 @@
         <v>46055</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K6" s="15" t="s">
         <v>15</v>
@@ -1584,7 +1591,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C7" s="15">
         <v>2026</v>
@@ -1599,10 +1606,10 @@
         <v>46059</v>
       </c>
       <c r="G7" s="15">
-        <v>9444</v>
+        <v>9935</v>
       </c>
       <c r="H7" s="14">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="I7" s="13">
         <v>46055</v>
@@ -1619,7 +1626,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C8" s="15">
         <v>2026</v>
@@ -1634,10 +1641,10 @@
         <v>46059</v>
       </c>
       <c r="G8" s="15">
-        <v>9457</v>
+        <v>9140</v>
       </c>
       <c r="H8" s="14">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I8" s="13">
         <v>46055</v>
@@ -1669,7 +1676,7 @@
         <v>46059</v>
       </c>
       <c r="G9" s="15">
-        <v>9737</v>
+        <v>9262</v>
       </c>
       <c r="H9" s="14">
         <v>46023</v>
@@ -1704,7 +1711,7 @@
         <v>46059</v>
       </c>
       <c r="G10" s="15">
-        <v>9804</v>
+        <v>9737</v>
       </c>
       <c r="H10" s="14">
         <v>46023</v>
@@ -1713,7 +1720,7 @@
         <v>46055</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>15</v>
@@ -1724,7 +1731,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="15">
         <v>2026</v>
@@ -1739,10 +1746,10 @@
         <v>46059</v>
       </c>
       <c r="G11" s="15">
-        <v>9935</v>
+        <v>9804</v>
       </c>
       <c r="H11" s="14">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="I11" s="13">
         <v>46055</v>
@@ -1767,6 +1774,11 @@
       <c r="F15" s="5"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K15" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K15">
+      <sortCondition ref="B1:B15"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
